--- a/erp-server/erp-server-oms/src/main/resources/excel/ShopInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/ShopInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25200" windowHeight="11850"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>平台</t>
   </si>
@@ -59,6 +59,21 @@
     <t>修改时间</t>
   </si>
   <si>
+    <t>结算币别</t>
+  </si>
+  <si>
+    <t>交易币别</t>
+  </si>
+  <si>
+    <t>启用时间</t>
+  </si>
+  <si>
+    <t>停用时间</t>
+  </si>
+  <si>
+    <t>店铺站点</t>
+  </si>
+  <si>
     <t>{.platformName}</t>
   </si>
   <si>
@@ -87,6 +102,21 @@
   </si>
   <si>
     <t>{.updateTime}</t>
+  </si>
+  <si>
+    <t>{.settlementCurrency}</t>
+  </si>
+  <si>
+    <t>{.tradeCurrency}</t>
+  </si>
+  <si>
+    <t>{.enableTime}</t>
+  </si>
+  <si>
+    <t>{.downTime}</t>
+  </si>
+  <si>
+    <t>{.dictCountryCode}</t>
   </si>
 </sst>
 </file>
@@ -1057,14 +1087,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="7" width="20.125" customWidth="1"/>
     <col min="8" max="10" width="20.625" customWidth="1"/>
+    <col min="11" max="11" width="20.875" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="13.125" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1095,37 +1130,67 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/ShopInfo.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/ShopInfo.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>平台</t>
   </si>
@@ -71,9 +71,6 @@
     <t>停用时间</t>
   </si>
   <si>
-    <t>店铺站点</t>
-  </si>
-  <si>
     <t>{.platformName}</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
   </si>
   <si>
     <t>{.downTime}</t>
-  </si>
-  <si>
-    <t>{.dictCountryCode}</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1081,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="7" width="20.125" customWidth="1"/>
@@ -1096,10 +1090,9 @@
     <col min="12" max="12" width="17" customWidth="1"/>
     <col min="13" max="13" width="13.125" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1142,55 +1135,49 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
